--- a/songs/BloodyMary_v1/quelle/struktur.xlsx
+++ b/songs/BloodyMary_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>10</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>114</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.125</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>BLACK</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(1840, 3)   (Matrix: progScrollText("Bloody Mary by Lady Gaga", 17500, 90, getRandomColor(), 3))</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(1840, 3)   (Matrix: progScrollText("Bloody Mary by Lady Gaga", 17500, 90, getRandomColor(), 3))</t>
         </is>
@@ -551,13 +566,19 @@
           <t>synth intro</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(16840, 6, 525, true)   (Matrix: progBlack(1180, 6))</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(16840, 6, 525, true)   (Matrix: progBlack(1180, 6))</t>
         </is>
@@ -572,13 +593,19 @@
           <t>verse 1</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(16830, 4, 9)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progPalette(16830, 4, 9)</t>
         </is>
@@ -593,13 +620,19 @@
           <t>dance dance</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(16840, 12, 525, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progStrobo(16840, 12, 525, getRandomCRGB())</t>
         </is>
@@ -614,13 +647,19 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(16840, 525, 15, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16840, 525, 15, 5, 26, 5, true, 3)</t>
         </is>
@@ -635,13 +674,19 @@
           <t>chorus instrumental</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8420, 3, 18)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8420, 3, 18)</t>
         </is>
@@ -656,13 +701,19 @@
           <t>FX</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(2105, 10, 21)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progPalette(2105, 10, 21)</t>
         </is>
@@ -677,13 +728,19 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlingBlingColoring(16830, 24, 3000)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(16830, 24, 3000)</t>
         </is>
@@ -698,13 +755,19 @@
           <t>dance dance</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(16840, 27, 525, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progStrobo(16840, 27, 525, getRandomCRGB())</t>
         </is>
@@ -719,13 +782,19 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(16845, 525, 30, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16845, 525, 30, 5, 26, 5, false, 4)</t>
         </is>
@@ -740,13 +809,19 @@
           <t>synth break</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(8350, 33, 525, true)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(8350, 33, 525, true)</t>
         </is>
@@ -761,13 +836,19 @@
           <t>git vs synth (git)</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1050, 36, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1050, 36, 50, getRandomCRGB())</t>
         </is>
@@ -782,13 +863,19 @@
           <t>git vs synth (synth)</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1045, 4, 39)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 39)</t>
         </is>
@@ -803,13 +890,19 @@
           <t>git vs synth (git)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1050, 42, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1050, 42, 50, getRandomCRGB())</t>
         </is>
@@ -824,13 +917,19 @@
           <t>git vs synth (synth)</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1045, 4, 45)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 45)</t>
         </is>
@@ -845,13 +944,19 @@
           <t>git vs synth (git)</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1050, 48, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1050, 48, 50, getRandomCRGB())</t>
         </is>
@@ -866,13 +971,19 @@
           <t>git vs synth (synth)</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1045, 4, 51)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 51)</t>
         </is>
@@ -887,13 +998,19 @@
           <t>git vs synth (git)</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1055, 54, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1055, 54, 50, getRandomCRGB())</t>
         </is>
@@ -908,13 +1025,19 @@
           <t>git vs synth (synth)</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1045, 4, 57)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 57)</t>
         </is>
@@ -929,13 +1052,19 @@
           <t>git vs synth (git)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1055, 60, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1055, 60, 50, getRandomCRGB())</t>
         </is>
@@ -950,13 +1079,19 @@
           <t>git vs synth (synth)</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1045, 4, 63)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 63)</t>
         </is>
@@ -971,13 +1106,19 @@
           <t>git vs synth (git)</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1055, 66, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1055, 66, 50, getRandomCRGB())</t>
         </is>
@@ -992,13 +1133,19 @@
           <t>git vs synth (synth)</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1045, 4, 69)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 69)</t>
         </is>
@@ -1013,13 +1160,19 @@
           <t>git vs synth (git)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1055, 72, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1055, 72, 50, getRandomCRGB())</t>
         </is>
@@ -1034,13 +1187,19 @@
           <t>git vs synth (synth)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1045, 4, 75)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 75)</t>
         </is>
@@ -1055,13 +1214,19 @@
           <t>git vs synth (git)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1055, 78, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1055, 78, 50, getRandomCRGB())</t>
         </is>
@@ -1076,13 +1241,19 @@
           <t>git vs synth (synth)</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(1045, 4, 81)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 81)</t>
         </is>
@@ -1097,13 +1268,19 @@
           <t>instrumental</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(16845, 84, 50, true, true)</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16845, 84, 50, true, true)</t>
         </is>
@@ -1118,13 +1295,19 @@
           <t>dance dance</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(16840, 87, 525, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>progStrobo(16840, 87, 525, getRandomCRGB())</t>
         </is>
@@ -1139,13 +1322,19 @@
           <t>chorus a</t>
         </is>
       </c>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(16845, 525, 90, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16845, 525, 90, 5, 26, 5, true, 3)</t>
         </is>
@@ -1160,13 +1349,19 @@
           <t>chorus b</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(16840, 8, 96)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(16840, 8, 96)</t>
         </is>
@@ -1181,13 +1376,19 @@
           <t>outro</t>
         </is>
       </c>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+! nur im Excel - der alte Code geht hier schon in Schwarz</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
@@ -1207,10 +1408,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/BloodyMary_v1/quelle/struktur.xlsx
+++ b/songs/BloodyMary_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>66.5</v>
+        <v>67.5</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>67.5</v>
+        <v>68.5</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>68.5</v>
+        <v>69.5</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>69.5</v>
+        <v>70.5</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>70.5</v>
+        <v>71.5</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>71.5</v>
+        <v>72.5</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>73.5</v>
+        <v>74.5</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>

--- a/songs/BloodyMary_v1/quelle/struktur.xlsx
+++ b/songs/BloodyMary_v1/quelle/struktur.xlsx
@@ -436,16 +436,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +471,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -481,6 +483,7 @@
         <v>114</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -492,6 +495,7 @@
         <v>0.125</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -516,15 +520,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -546,12 +555,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(1840, 3)   (Matrix: progScrollText("Bloody Mary by Lady Gaga", 17500, 90, getRandomColor(), 3))</t>
         </is>
@@ -573,12 +583,17 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Szene Glow, ROYAL, Farbwanderung (triad, 2 Takte): füllt sich langsam in Blau/Lila und wandert nach Pink - dunkler Einstieg statt Linien im Beat.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(16840, 6, 525, true)   (Matrix: progBlack(1180, 6))</t>
         </is>
@@ -600,12 +615,17 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Szene Rain, RED: blutrote Leuchtspuren, weich eingeblendet (Übergang fade, 2 Beats).</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>progPalette(16830, 4, 9)</t>
         </is>
@@ -627,12 +647,18 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Szene Call Response, RETRO (rot/weiß/blau): die Bühnenhälften blitzen abwechselnd im Beat. Als Motiv bei allen drei "dance dance" gleich.
+Dazu auf der Matrix der Text "DANCE" im Beat über der Szene.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progStrobo(16840, 12, 525, getRandomCRGB())</t>
         </is>
@@ -654,12 +680,17 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Stern bleibt, aber in festen Farben (NEON) und mit weichen Farbwechseln (soft 40). Blinder auf den Einsatz (2 Beats).</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16840, 525, 15, 5, 26, 5, true, 3)</t>
         </is>
@@ -681,12 +712,13 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8420, 3, 18)</t>
         </is>
@@ -708,12 +740,17 @@
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Blinder auf die 1 (Takt 38), klingt über den ganzen Takt aus, darunter Schwarz - Atempause vor verse 2.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progPalette(2105, 10, 21)</t>
         </is>
@@ -735,12 +772,17 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Szene DNA Flip Scroll, ROYAL: Helix auf der Matrix, alle anderen pulsieren einmal je Takt (neue Szene, bisher in keinem Song).</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(16830, 24, 3000)</t>
         </is>
@@ -762,12 +804,17 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Motiv wie beim ersten Mal (Call Response, RETRO, Text DANCE).</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progStrobo(16840, 27, 525, getRandomCRGB())</t>
         </is>
@@ -789,12 +836,17 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Stern wie chorus 1, eine Stufe mehr: die Lampen blitzen weiß auf 2 und 4 (Blinder nur Lampen, wie Billie Jean chorus 2).</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16845, 525, 30, 5, 26, 5, false, 4)</t>
         </is>
@@ -816,12 +868,17 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Szene Colors Wave, NEON, soft 60: die Farbe wandert pro Beat weich von Gerät zu Gerät.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(8350, 33, 525, true)</t>
         </is>
@@ -843,12 +900,17 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Idee für alle 8 Paare: "git" = Strobo nur auf Gitarre und Bass (only guitar), Rest dunkel; "synth" = Einzelblitze nur auf Lampen und Matrix. So sieht man das Duell auch auf der Bühne.</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1050, 36, 50, getRandomCRGB())</t>
         </is>
@@ -870,12 +932,17 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>siehe Zeile darüber: Einzelblitze nur auf Lampen und Matrix, Gitarre und Bass dunkel.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 39)</t>
         </is>
@@ -897,12 +964,13 @@
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1050, 42, 50, getRandomCRGB())</t>
         </is>
@@ -924,12 +992,13 @@
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 45)</t>
         </is>
@@ -951,12 +1020,13 @@
         </is>
       </c>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1050, 48, 50, getRandomCRGB())</t>
         </is>
@@ -978,12 +1048,13 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 51)</t>
         </is>
@@ -1005,12 +1076,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1055, 54, 50, getRandomCRGB())</t>
         </is>
@@ -1032,12 +1104,13 @@
         </is>
       </c>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 57)</t>
         </is>
@@ -1059,12 +1132,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1055, 60, 50, getRandomCRGB())</t>
         </is>
@@ -1086,12 +1160,13 @@
         </is>
       </c>
       <c r="D26" s="6" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 63)</t>
         </is>
@@ -1113,12 +1188,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1055, 66, 50, getRandomCRGB())</t>
         </is>
@@ -1140,12 +1216,13 @@
         </is>
       </c>
       <c r="D28" s="6" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 69)</t>
         </is>
@@ -1167,12 +1244,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1055, 72, 50, getRandomCRGB())</t>
         </is>
@@ -1194,12 +1272,13 @@
         </is>
       </c>
       <c r="D30" s="6" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 75)</t>
         </is>
@@ -1221,12 +1300,13 @@
         </is>
       </c>
       <c r="D31" s="6" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1055, 78, 50, getRandomCRGB())</t>
         </is>
@@ -1248,12 +1328,17 @@
         </is>
       </c>
       <c r="D32" s="6" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Letztes Paar: starker Blinder auf die letzte Viertel (Takt 74,75) als Absprung ins Instrumental.</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(1045, 4, 81)</t>
         </is>
@@ -1275,12 +1360,17 @@
         </is>
       </c>
       <c r="D33" s="6" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Wasserringe bleiben, weich eingeblendet (fade, 2 Beats). Falls hier ein Gitarrensolo liegt: Szene Solo Gitarre, SUNSET.</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16845, 84, 50, true, true)</t>
         </is>
@@ -1302,12 +1392,17 @@
         </is>
       </c>
       <c r="D34" s="6" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Motiv wie vorher, dazu baut sich über den ganzen Part ein Glitzern auf (Ebene Sparkle, fade_in 8 Takte) - Anlauf zum letzten Chorus.</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>progStrobo(16840, 87, 525, getRandomCRGB())</t>
         </is>
@@ -1329,12 +1424,17 @@
         </is>
       </c>
       <c r="D35" s="6" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, FIRE (eine Stufe wärmer), Blinder auf den Einsatz; Ende des 4. Takts drei kurze Blinder auf drei Vierteln (Takt 94,5 / 94,75 / 95) wie in Tell It To My Heart.</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(16845, 525, 90, 5, 26, 5, true, 3)</t>
         </is>
@@ -1356,12 +1456,17 @@
         </is>
       </c>
       <c r="D36" s="6" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Szene Sparkle, FIRE; starker Blinder auf der letzten Viertel (Takt 106,75), der ins Outro ausklingt (carry).</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(16840, 8, 96)</t>
         </is>
@@ -1383,12 +1488,17 @@
         </is>
       </c>
       <c r="D37" s="6" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Szene Fadeout, RED: Rot blendet über die 2 Takte weich nach Schwarz (im alten Code war hier schon Schwarz).</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>! nur im Excel - der alte Code geht hier schon in Schwarz</t>
         </is>
@@ -1408,10 +1518,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>0</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <f>$C$3</f>
         <v/>
       </c>
